--- a/backtest_runs/20260410_193731/by_symbol/DWSM/DWSM.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/DWSM/DWSM.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-7307.779999999998</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>98846.14000000001</v>
@@ -679,7 +679,7 @@
         <v>-5000.060000000013</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>93846.07999999999</v>
@@ -771,7 +771,7 @@
         <v>-8269.330000000011</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>92884.53</v>
@@ -817,7 +817,7 @@
         <v>-384.6199999999918</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>92499.91</v>
@@ -909,7 +909,7 @@
         <v>-1730.789999999997</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>94038.39000000001</v>
@@ -955,7 +955,7 @@
         <v>-4423.130000000008</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>89615.25999999999</v>
@@ -1185,7 +1185,7 @@
         <v>-3653.88999999999</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>91538.36000000002</v>
@@ -1277,7 +1277,7 @@
         <v>-6153.920000000006</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>86345.99000000001</v>
@@ -1461,7 +1461,7 @@
         <v>-2307.720000000002</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>92884.53</v>
@@ -1507,7 +1507,7 @@
         <v>-769.2400000000007</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>92115.28999999999</v>
@@ -1645,7 +1645,7 @@
         <v>-6730.849999999993</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>95576.87000000001</v>
